--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Com\Desktop\개발\포크\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Com\Desktop\Project\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
   <si>
     <t>Item_Equip_Hat_1</t>
   </si>
@@ -138,6 +138,41 @@
   </si>
   <si>
     <t>당근이다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Icon/Icon_Item_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Trap</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>_1</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>곰덫이다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>곰덫</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Trap_1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -145,7 +180,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -170,6 +205,12 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -257,7 +298,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -287,6 +328,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -472,7 +517,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -481,7 +526,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -962,14 +1007,30 @@
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="A10" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="4">
+        <v>20</v>
+      </c>
+      <c r="G10" s="4">
+        <v>100</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -2119,6 +2180,6 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="71">
   <si>
     <t>Item_Equip_Hat_1</t>
   </si>
@@ -158,6 +158,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>_1</t>
     </r>
@@ -173,6 +174,114 @@
   </si>
   <si>
     <t>Item_Trap_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor/RoyalTunic</t>
+  </si>
+  <si>
+    <t>로얄튜닉</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_RoyalTunic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots/BattleguardArmor</t>
+  </si>
+  <si>
+    <t>경비대부츠</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>경비대원의 부츠이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>로얄튜닉이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_BattleguardArmor</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bow/HunterBow</t>
+  </si>
+  <si>
+    <t>Item_HunterBow</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>사냥꾼의활</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>어느 사냥꾼이 쓰던 활이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet/ScoutHelm</t>
+  </si>
+  <si>
+    <t>Item_ScoutHelm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>수색대의투구</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>어느 수색대원의 투구이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무대형망치</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeleeWeapon2H/TwoHandedWoodenMace</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_TwoHandedWoodenMace</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeleeWeapon2H/OldPoleaxe</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_OldPoleaxe</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>녹슨도끼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>관리를 안해 녹슨 도끼이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무로 된 대형망치이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring/GoldenRing</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_GoldenRing</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>황금반지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>순금으로 된 황금반지이다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -298,7 +407,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -314,8 +423,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -334,6 +441,7 @@
     <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -795,29 +903,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A3" s="11" t="s">
+    <row r="3" spans="1:13" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A3" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="11" t="s">
         <v>24</v>
       </c>
     </row>
@@ -945,7 +1053,7 @@
       <c r="M7" s="4"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="13" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -976,7 +1084,7 @@
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -1007,7 +1115,7 @@
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="16" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1028,7 +1136,7 @@
       <c r="G10" s="4">
         <v>100</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="15" t="s">
         <v>39</v>
       </c>
       <c r="I10" s="4"/>
@@ -1038,14 +1146,30 @@
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="A11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4">
+        <v>0</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>43</v>
+      </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -1053,14 +1177,30 @@
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="A12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -1068,14 +1208,30 @@
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="A13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -1083,14 +1239,30 @@
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="A14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>55</v>
+      </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -1098,14 +1270,30 @@
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="4">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>60</v>
+      </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -1113,104 +1301,201 @@
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
+      <c r="A16" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A17" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="4">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A20" s="17"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A21" s="17"/>
+      <c r="B21" s="17"/>
+      <c r="C21" s="17"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A22" s="17"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A23" s="17"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A24" s="17"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A26" s="17"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="17"/>
+      <c r="D26" s="17"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A27" s="17"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="17"/>
+      <c r="D27" s="17"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A28" s="17"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="17"/>
+      <c r="D28" s="17"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="81">
   <si>
     <t>Item_Equip_Hat_1</t>
   </si>
@@ -82,12 +82,6 @@
   </si>
   <si>
     <t>캐릭터 고유 ID</t>
-  </si>
-  <si>
-    <t>Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Item_Corn_1</t>
   </si>
   <si>
     <t>Description</t>
@@ -282,6 +276,570 @@
   </si>
   <si>
     <t>순금으로 된 황금반지이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>seItemType</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tatChangeAtk</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tatChangeHp</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SummonMonster</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>U</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>seItemParaMeter</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>RadomItemBox</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파라미터는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>획득할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이템</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Id </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>리스트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+StatChangeAtk</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파라미터는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>음수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양수로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ATK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">디버프
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>StatChangeHp</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파라미터는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>음수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양수로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> HP </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>버프</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">디버프
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Summon </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>파라미터는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소환할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>있는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>몬스터의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">리스트
+</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Corn_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Gold_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mob_bear_1:2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RandomItemBox</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -289,7 +847,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -320,6 +878,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="10">
@@ -407,7 +972,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -442,6 +1007,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -865,7 +1434,9 @@
     <col min="4" max="4" width="26.5703125" style="2" customWidth="1"/>
     <col min="5" max="7" width="12.5703125" style="2"/>
     <col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="12.5703125" style="2"/>
+    <col min="9" max="9" width="12.5703125" style="2"/>
+    <col min="10" max="10" width="41.85546875" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="12.5703125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1">
@@ -876,6 +1447,9 @@
       <c r="C1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="J1" s="19" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="2" spans="1:13" ht="12.75">
       <c r="A2" s="1" t="s">
@@ -894,24 +1468,30 @@
         <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="3" spans="1:13" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>14</v>
@@ -926,7 +1506,13 @@
         <v>15</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>24</v>
+        <v>22</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1">
@@ -934,7 +1520,7 @@
         <v>16</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>2</v>
@@ -952,20 +1538,24 @@
         <v>100</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>78</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>13</v>
@@ -983,7 +1573,7 @@
         <v>1000</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -1014,19 +1604,21 @@
         <v>1</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>70</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>4</v>
@@ -1046,7 +1638,9 @@
       <c r="H7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I7" s="4"/>
+      <c r="I7" s="15" t="s">
+        <v>71</v>
+      </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -1054,13 +1648,13 @@
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>11</v>
@@ -1075,23 +1669,27 @@
         <v>100</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>79</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1">
       <c r="A9" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>36</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>11</v>
@@ -1106,7 +1704,7 @@
         <v>100</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -1116,13 +1714,13 @@
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>11</v>
@@ -1137,7 +1735,7 @@
         <v>100</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -1147,13 +1745,13 @@
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>11</v>
@@ -1168,7 +1766,7 @@
         <v>0</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -1178,13 +1776,13 @@
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>11</v>
@@ -1199,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1209,13 +1807,13 @@
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>11</v>
@@ -1230,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -1240,13 +1838,13 @@
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>11</v>
@@ -1261,7 +1859,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -1271,13 +1869,13 @@
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>11</v>
@@ -1292,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1302,13 +1900,13 @@
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1">
       <c r="A16" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="17" t="s">
         <v>63</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>65</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>11</v>
@@ -1323,18 +1921,18 @@
         <v>0</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>68</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>70</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>11</v>
@@ -1349,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -19,23 +19,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="81">
-  <si>
-    <t>Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Corn</t>
-  </si>
-  <si>
-    <t>상자다. 딱히 의미가 있진 않다.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="82">
   <si>
     <t>string</t>
   </si>
   <si>
-    <t>옥수수다</t>
-  </si>
-  <si>
     <t>(name)</t>
   </si>
   <si>
@@ -45,39 +33,18 @@
     <t>Grade</t>
   </si>
   <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Legend</t>
-  </si>
-  <si>
-    <t>의문의 모자</t>
-  </si>
-  <si>
     <t>Normal</t>
   </si>
   <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>지역에 나타나는 금화</t>
-  </si>
-  <si>
     <t>ItemType</t>
   </si>
   <si>
     <t>SellingPrice</t>
   </si>
   <si>
-    <t>Item_DummyBox_1</t>
-  </si>
-  <si>
     <t>MaxStackCount</t>
   </si>
   <si>
-    <t>착용하면 공격력이 강해진다.</t>
-  </si>
-  <si>
     <t>캐릭터 전체 컨셉이나 스토리</t>
   </si>
   <si>
@@ -90,87 +57,12 @@
     <t>IconPath</t>
   </si>
   <si>
-    <t>상자</t>
-  </si>
-  <si>
-    <t>옥수수</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>화폐</t>
-  </si>
-  <si>
-    <t>Item_Potato_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Box_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Gold_1</t>
-  </si>
-  <si>
-    <t>Icon/Icon_Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t>감자</t>
-  </si>
-  <si>
-    <t>감자다. 딱히 의미가 있진 않다.</t>
-  </si>
-  <si>
-    <t>Item_Carrot_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>당근</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>당근이다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Icon/Icon_Item_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Trap</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_1</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>곰덫이다</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>곰덫</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Trap_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Armor/RoyalTunic</t>
   </si>
   <si>
@@ -291,40 +183,6 @@
       </rPr>
       <t>seItemType</t>
     </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tatChangeAtk</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>S</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tatChangeHp</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>SummonMonster</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -823,23 +681,314 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Item_Corn_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Gold_1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>mob_bear_1:2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RandomItemBox</t>
+    <t>MeleeWeapon2H/AriostinGreatsword</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_AriostinGreatsword</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeleeWeapon1H/VikingAxe</t>
+  </si>
+  <si>
+    <t>Item_VikingAxe</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeleeWeapon1H/SwampWarriorSpear</t>
+  </si>
+  <si>
+    <t>Item_SwampWarriorSpear</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeleeWeapon1H/WoodenClub</t>
+  </si>
+  <si>
+    <t>Item_WoodenClub</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Armor/DarkMountain</t>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tem_DarkMountain</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots/GreyKnight</t>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tem_GreyKnight</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>바이킹의도끼</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>늪지대전사의창</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무클럽</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>검은색흉갑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>판금장화</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>양손검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>양손검이다.무게가 무거워 한손으로 들기 힘들어보인다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>어느 한 바이킹이 애용하던 도끼이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>늪지대전사가 쓰던 창이다..많이 낡아보인다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무로 만든 클럽이다..맞으면 아플거 같다</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검은색</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>흉갑이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입으면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>든든하다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>판금장화이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>많이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무거워</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보인다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeleeWeapon1H/BronzeDagger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_BronzeDagger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>황동단검</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>황동 단검이다.한번찌르면 못쓸거같다..</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boots/DarkMountain</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>검은색신발</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>검은색 신발이다.생각보다 착용감이 좋다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Helmet/ManticoreHelmet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_ManticoreHelmet</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>만티코어헬멧</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>만티코어 헬멧이다. 쓰기만 했는데 용기가 차오른다..!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_DarkMountainBoots</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -972,7 +1121,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1011,6 +1160,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1441,139 +1591,135 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="12.75">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:13" s="10" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="B3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>15</v>
-      </c>
       <c r="H3" s="11" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F4" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G4" s="4">
-        <v>100</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>78</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="5"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -1583,64 +1729,60 @@
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F6" s="4">
         <v>0</v>
       </c>
       <c r="G6" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="15" t="s">
-        <v>70</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="I6" s="15"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="1:13" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F7" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4">
-        <v>20</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>71</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="15"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -1648,63 +1790,59 @@
     </row>
     <row r="8" spans="1:13" ht="15.75" customHeight="1">
       <c r="A8" s="13" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>33</v>
+        <v>67</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F8" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>79</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F9" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G9" s="4">
-        <v>100</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>31</v>
+        <v>0</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>74</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -1714,28 +1852,28 @@
     </row>
     <row r="10" spans="1:13" ht="15.75" customHeight="1">
       <c r="A10" s="16" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F10" s="4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G10" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -1744,20 +1882,20 @@
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>47</v>
+      <c r="A11" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>68</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F11" s="4">
         <v>0</v>
@@ -1765,8 +1903,8 @@
       <c r="G11" s="4">
         <v>0</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>41</v>
+      <c r="H11" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -1775,20 +1913,20 @@
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>46</v>
+      <c r="A12" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>69</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F12" s="4">
         <v>0</v>
@@ -1796,8 +1934,8 @@
       <c r="G12" s="4">
         <v>0</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>44</v>
+      <c r="H12" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1806,20 +1944,20 @@
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>52</v>
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F13" s="4">
         <v>0</v>
@@ -1828,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -1837,20 +1975,20 @@
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>56</v>
+      <c r="A14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F14" s="4">
         <v>0</v>
@@ -1859,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -1868,20 +2006,20 @@
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>64</v>
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F15" s="4">
         <v>0</v>
@@ -1889,8 +2027,8 @@
       <c r="G15" s="4">
         <v>0</v>
       </c>
-      <c r="H15" s="15" t="s">
-        <v>58</v>
+      <c r="H15" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1899,20 +2037,20 @@
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A16" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>63</v>
+      <c r="A16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F16" s="4">
         <v>0</v>
@@ -1920,25 +2058,25 @@
       <c r="G16" s="4">
         <v>0</v>
       </c>
-      <c r="H16" s="15" t="s">
-        <v>60</v>
+      <c r="H16" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A17" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>68</v>
+      <c r="A17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F17" s="4">
         <v>0</v>
@@ -1946,29 +2084,61 @@
       <c r="G17" s="4">
         <v>0</v>
       </c>
-      <c r="H17" s="17" t="s">
-        <v>65</v>
+      <c r="H17" s="15" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
+      <c r="A18" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
+      <c r="A19" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="17"/>
